--- a/unilabos/devices/workstation/szlab_poly_studio/robot/robot_only.xlsx
+++ b/unilabos/devices/workstation/szlab_poly_studio/robot/robot_only.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yinziqi/Desktop/robot/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EE9D4DF-FC0E-DF40-80B1-17A1D9510A4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BF8EA3B-6EAE-FB4C-8F5D-6AAB3E40661E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{F3F4E3D6-EB34-F849-953C-B1ECC65BE545}"/>
+    <workbookView xWindow="14280" yWindow="860" windowWidth="15960" windowHeight="18780" xr2:uid="{F3F4E3D6-EB34-F849-953C-B1ECC65BE545}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="81">
   <si>
     <t>任务号</t>
   </si>
@@ -233,12 +233,6 @@
     <t>S11取放料编号</t>
   </si>
   <si>
-    <t>PLC_R任务号</t>
-  </si>
-  <si>
-    <t>INT</t>
-  </si>
-  <si>
     <t>不保持</t>
   </si>
   <si>
@@ -251,16 +245,47 @@
     <t>保持</t>
   </si>
   <si>
-    <t>PC-PLC</t>
-  </si>
-  <si>
     <t>S01出入料产品</t>
   </si>
   <si>
-    <t xml:space="preserve">PC-PLC </t>
-  </si>
-  <si>
-    <t xml:space="preserve">PC-PLC  </t>
+    <t>Robot_Home</t>
+  </si>
+  <si>
+    <t>BOOL</t>
+  </si>
+  <si>
+    <t>OFF</t>
+  </si>
+  <si>
+    <t>私有</t>
+  </si>
+  <si>
+    <t>Robot工位 PLC-PC</t>
+  </si>
+  <si>
+    <t>Robot工位 PC-PLC</t>
+  </si>
+  <si>
+    <t>DINT</t>
+  </si>
+  <si>
+    <t>Robot工位 PLC-PC_x0006_</t>
+  </si>
+  <si>
+    <t>Robot_任务允许写入</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Robot_任务写入完成</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Robot_任务完成</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DINT</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -666,100 +691,100 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1096,9 +1121,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2925983E-F1F3-164B-9C06-8B9BE8886E2A}">
-  <dimension ref="A1:H42"/>
+  <dimension ref="A1:H46"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
+    <col min="1" max="1" width="9" customWidth="1"/>
+    <col min="2" max="2" width="24.6640625" customWidth="1"/>
     <col min="4" max="4" width="27.6640625" customWidth="1"/>
     <col min="5" max="5" width="35.1640625" customWidth="1"/>
     <col min="6" max="6" width="48.33203125" customWidth="1"/>
@@ -1106,124 +1133,124 @@
   <sheetData>
     <row r="1" spans="1:6" ht="25" thickBot="1">
       <c r="A1" s="1"/>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="3"/>
-      <c r="D1" s="4" t="s">
+      <c r="C1" s="25"/>
+      <c r="D1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="5"/>
-      <c r="F1" s="6"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="4"/>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="1"/>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="9">
+      <c r="D2" s="6">
         <v>1</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="F2" s="8" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="17" thickBot="1">
       <c r="A3" s="1"/>
-      <c r="B3" s="12"/>
-      <c r="C3" s="13"/>
-      <c r="D3" s="14">
+      <c r="B3" s="9"/>
+      <c r="C3" s="27"/>
+      <c r="D3" s="10">
         <v>2</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="E3" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="F3" s="8" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="1"/>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="14">
+      <c r="D4" s="10">
         <v>3</v>
       </c>
-      <c r="E4" s="17" t="s">
+      <c r="E4" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="18" t="s">
+      <c r="F4" s="30" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="1"/>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="13"/>
-      <c r="D5" s="9">
+      <c r="C5" s="27"/>
+      <c r="D5" s="6">
         <v>4</v>
       </c>
-      <c r="E5" s="19"/>
-      <c r="F5" s="18"/>
+      <c r="E5" s="22"/>
+      <c r="F5" s="30"/>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="1"/>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="16" t="s">
+      <c r="C6" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="14">
+      <c r="D6" s="10">
         <v>5</v>
       </c>
-      <c r="E6" s="20" t="s">
+      <c r="E6" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="11" t="s">
+      <c r="F6" s="8" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="1"/>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="13"/>
-      <c r="D7" s="14">
+      <c r="C7" s="27"/>
+      <c r="D7" s="10">
         <v>6</v>
       </c>
-      <c r="E7" s="20" t="s">
+      <c r="E7" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="F7" s="21" t="s">
+      <c r="F7" s="13" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="1"/>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="16" t="s">
+      <c r="C8" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="9">
+      <c r="D8" s="6">
         <v>7</v>
       </c>
-      <c r="E8" s="22" t="s">
+      <c r="E8" s="21" t="s">
         <v>21</v>
       </c>
       <c r="F8" s="23" t="s">
@@ -1232,82 +1259,82 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="1"/>
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="13"/>
-      <c r="D9" s="14">
+      <c r="C9" s="27"/>
+      <c r="D9" s="10">
         <v>8</v>
       </c>
-      <c r="E9" s="19"/>
+      <c r="E9" s="22"/>
       <c r="F9" s="23"/>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="1"/>
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="14">
+      <c r="D10" s="10">
         <v>9</v>
       </c>
-      <c r="E10" s="20"/>
-      <c r="F10" s="21"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="13"/>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="1"/>
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="13"/>
-      <c r="D11" s="9">
+      <c r="C11" s="27"/>
+      <c r="D11" s="6">
         <v>10</v>
       </c>
-      <c r="E11" s="20"/>
-      <c r="F11" s="21"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="13"/>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="1"/>
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="14">
+      <c r="D12" s="10">
         <v>11</v>
       </c>
-      <c r="E12" s="20"/>
-      <c r="F12" s="21"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="13"/>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="1"/>
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="13"/>
-      <c r="D13" s="14">
+      <c r="C13" s="27"/>
+      <c r="D13" s="10">
         <v>12</v>
       </c>
-      <c r="E13" s="20"/>
-      <c r="F13" s="21"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="13"/>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B14" s="24" t="s">
+      <c r="B14" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="C14" s="25" t="s">
+      <c r="C14" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="D14" s="9">
+      <c r="D14" s="6">
         <v>13</v>
       </c>
-      <c r="E14" s="22" t="s">
+      <c r="E14" s="21" t="s">
         <v>32</v>
       </c>
       <c r="F14" s="23" t="s">
@@ -1318,30 +1345,30 @@
       <c r="A15" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B15" s="24" t="s">
+      <c r="B15" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="C15" s="25"/>
-      <c r="D15" s="14">
+      <c r="C15" s="20"/>
+      <c r="D15" s="10">
         <v>14</v>
       </c>
-      <c r="E15" s="19"/>
+      <c r="E15" s="22"/>
       <c r="F15" s="23"/>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B16" s="24" t="s">
+      <c r="B16" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="C16" s="25" t="s">
+      <c r="C16" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="D16" s="14">
+      <c r="D16" s="10">
         <v>15</v>
       </c>
-      <c r="E16" s="22" t="s">
+      <c r="E16" s="21" t="s">
         <v>37</v>
       </c>
       <c r="F16" s="23" t="s">
@@ -1352,511 +1379,606 @@
       <c r="A17" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B17" s="24" t="s">
+      <c r="B17" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="C17" s="25"/>
-      <c r="D17" s="9">
+      <c r="C17" s="20"/>
+      <c r="D17" s="6">
         <v>16</v>
       </c>
-      <c r="E17" s="19"/>
+      <c r="E17" s="22"/>
       <c r="F17" s="23"/>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="1"/>
-      <c r="B18" s="12" t="s">
+      <c r="B18" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="C18" s="25" t="s">
+      <c r="C18" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="D18" s="14">
+      <c r="D18" s="10">
         <v>17</v>
       </c>
-      <c r="E18" s="20" t="s">
+      <c r="E18" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="F18" s="26" t="s">
+      <c r="F18" s="15" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="1"/>
-      <c r="B19" s="12" t="s">
+      <c r="B19" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="C19" s="25"/>
-      <c r="D19" s="14">
+      <c r="C19" s="20"/>
+      <c r="D19" s="10">
         <v>18</v>
       </c>
-      <c r="E19" s="20" t="s">
+      <c r="E19" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="F19" s="26" t="s">
+      <c r="F19" s="15" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="1"/>
-      <c r="B20" s="12" t="s">
+      <c r="B20" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="C20" s="25" t="s">
+      <c r="C20" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="D20" s="9">
+      <c r="D20" s="6">
         <v>19</v>
       </c>
-      <c r="E20" s="20" t="s">
+      <c r="E20" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="F20" s="26" t="s">
+      <c r="F20" s="15" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="1"/>
-      <c r="B21" s="12" t="s">
+      <c r="B21" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="C21" s="25"/>
-      <c r="D21" s="14">
+      <c r="C21" s="20"/>
+      <c r="D21" s="10">
         <v>20</v>
       </c>
-      <c r="E21" s="20" t="s">
+      <c r="E21" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="F21" s="26" t="s">
+      <c r="F21" s="15" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="1"/>
-      <c r="B22" s="12" t="s">
+      <c r="B22" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="C22" s="25" t="s">
+      <c r="C22" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="D22" s="14">
+      <c r="D22" s="10">
         <v>21</v>
       </c>
-      <c r="E22" s="22" t="s">
+      <c r="E22" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="F22" s="27" t="s">
+      <c r="F22" s="32" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="1"/>
-      <c r="B23" s="12" t="s">
+      <c r="B23" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="C23" s="25"/>
-      <c r="D23" s="9">
+      <c r="C23" s="20"/>
+      <c r="D23" s="6">
         <v>22</v>
       </c>
-      <c r="E23" s="19"/>
-      <c r="F23" s="28"/>
+      <c r="E23" s="22"/>
+      <c r="F23" s="33"/>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="1"/>
-      <c r="B24" s="12" t="s">
+      <c r="B24" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="C24" s="25" t="s">
+      <c r="C24" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="D24" s="14">
+      <c r="D24" s="10">
         <v>23</v>
       </c>
-      <c r="E24" s="20" t="s">
+      <c r="E24" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="F24" s="11" t="s">
+      <c r="F24" s="8" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="17" thickBot="1">
       <c r="A25" s="1"/>
-      <c r="B25" s="29" t="s">
+      <c r="B25" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="C25" s="30"/>
-      <c r="D25" s="31">
+      <c r="C25" s="31"/>
+      <c r="D25" s="17">
         <v>24</v>
       </c>
-      <c r="E25" s="32" t="s">
+      <c r="E25" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="F25" s="33" t="s">
+      <c r="F25" s="19" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B27" t="s">
+        <v>69</v>
+      </c>
+      <c r="C27" t="s">
+        <v>70</v>
+      </c>
+      <c r="E27" t="s">
+        <v>71</v>
+      </c>
+      <c r="F27" t="s">
         <v>64</v>
       </c>
-      <c r="C27" t="s">
-        <v>65</v>
-      </c>
-      <c r="E27">
-        <v>0</v>
-      </c>
-      <c r="F27" t="s">
-        <v>66</v>
-      </c>
       <c r="G27" t="s">
-        <v>67</v>
+        <v>72</v>
+      </c>
+      <c r="H27" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B28" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="C28" t="s">
-        <v>65</v>
-      </c>
-      <c r="E28">
-        <v>0</v>
+        <v>70</v>
+      </c>
+      <c r="E28" t="s">
+        <v>71</v>
       </c>
       <c r="F28" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="G28" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H28" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B29" t="s">
+        <v>78</v>
+      </c>
+      <c r="C29" t="s">
+        <v>70</v>
+      </c>
+      <c r="E29" t="s">
         <v>71</v>
       </c>
-      <c r="C29" t="s">
-        <v>65</v>
-      </c>
-      <c r="E29">
-        <v>0</v>
-      </c>
       <c r="F29" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="G29" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H29" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B30" t="s">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C30" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="E30">
         <v>0</v>
       </c>
       <c r="F30" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G30" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="H30" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B31" t="s">
-        <v>14</v>
+        <v>66</v>
       </c>
       <c r="C31" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="E31">
         <v>0</v>
       </c>
       <c r="F31" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G31" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="H31" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B32" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="C32" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="E32">
         <v>0</v>
       </c>
       <c r="F32" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G32" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="H32" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B33" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="C33" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="E33">
         <v>0</v>
       </c>
       <c r="F33" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G33" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="H33" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B34" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="C34" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="E34">
         <v>0</v>
       </c>
       <c r="F34" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G34" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="H34" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B35" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="C35" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="E35">
         <v>0</v>
       </c>
       <c r="F35" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G35" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="H35" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B36" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="C36" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="E36">
         <v>0</v>
       </c>
       <c r="F36" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G36" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="H36" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="37" spans="1:8">
       <c r="A37">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B37" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="C37" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="E37">
         <v>0</v>
       </c>
       <c r="F37" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G37" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="H37" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B38" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="C38" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="E38">
         <v>0</v>
       </c>
       <c r="F38" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G38" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="H38" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="39" spans="1:8">
       <c r="A39">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B39" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="C39" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="E39">
         <v>0</v>
       </c>
       <c r="F39" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G39" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="H39" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B40" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="C40" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="E40">
         <v>0</v>
       </c>
       <c r="F40" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G40" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="H40" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B41" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="C41" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="E41">
         <v>0</v>
       </c>
       <c r="F41" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G41" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="H41" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B42" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="C42" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="E42">
         <v>0</v>
       </c>
       <c r="F42" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G42" t="s">
+        <v>65</v>
+      </c>
+      <c r="H42" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8">
+      <c r="A43">
+        <v>103</v>
+      </c>
+      <c r="B43" t="s">
+        <v>56</v>
+      </c>
+      <c r="C43" t="s">
+        <v>75</v>
+      </c>
+      <c r="E43">
+        <v>0</v>
+      </c>
+      <c r="F43" t="s">
         <v>67</v>
       </c>
-      <c r="H42" t="s">
-        <v>73</v>
+      <c r="G43" t="s">
+        <v>65</v>
+      </c>
+      <c r="H43" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8">
+      <c r="A44">
+        <v>104</v>
+      </c>
+      <c r="B44" t="s">
+        <v>61</v>
+      </c>
+      <c r="C44" t="s">
+        <v>75</v>
+      </c>
+      <c r="E44">
+        <v>0</v>
+      </c>
+      <c r="F44" t="s">
+        <v>67</v>
+      </c>
+      <c r="G44" t="s">
+        <v>65</v>
+      </c>
+      <c r="H44" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8">
+      <c r="A45">
+        <v>105</v>
+      </c>
+      <c r="B45" t="s">
+        <v>63</v>
+      </c>
+      <c r="C45" t="s">
+        <v>75</v>
+      </c>
+      <c r="E45">
+        <v>0</v>
+      </c>
+      <c r="F45" t="s">
+        <v>67</v>
+      </c>
+      <c r="G45" t="s">
+        <v>65</v>
+      </c>
+      <c r="H45" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8">
+      <c r="A46">
+        <v>106</v>
+      </c>
+      <c r="B46" t="s">
+        <v>79</v>
+      </c>
+      <c r="C46" t="s">
+        <v>75</v>
+      </c>
+      <c r="E46">
+        <v>0</v>
+      </c>
+      <c r="F46" t="s">
+        <v>67</v>
+      </c>
+      <c r="G46" t="s">
+        <v>72</v>
+      </c>
+      <c r="H46" t="s">
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -1870,11 +1992,6 @@
     <mergeCell ref="C22:C23"/>
     <mergeCell ref="E22:E23"/>
     <mergeCell ref="F22:F23"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="C12:C13"/>
     <mergeCell ref="C14:C15"/>
     <mergeCell ref="E14:E15"/>
     <mergeCell ref="F14:F15"/>
@@ -1884,6 +2001,11 @@
     <mergeCell ref="E4:E5"/>
     <mergeCell ref="F4:F5"/>
     <mergeCell ref="C6:C7"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="C12:C13"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
